--- a/scenarios/05_tom_optical_designer/5.4_jitter_induced_blur/outputs/jitter_tolerance_results.xlsx
+++ b/scenarios/05_tom_optical_designer/5.4_jitter_induced_blur/outputs/jitter_tolerance_results.xlsx
@@ -515,16 +515,16 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.37297</v>
+        <v>0.24092</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.64918</v>
+        <v>0.55474</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6.493</v>
+        <v>6.266</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -544,19 +544,19 @@
         <v>0.9809099999999999</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.36587</v>
+        <v>0.23633</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.64412</v>
+        <v>0.55147</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6.482</v>
+        <v>6.258</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.011</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         <v>0.92579</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.3453</v>
+        <v>0.22304</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.62944</v>
+        <v>0.54198</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>6.448</v>
+        <v>6.233</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.045</v>
+        <v>-0.034</v>
       </c>
     </row>
     <row r="7">
@@ -602,19 +602,19 @@
         <v>0.84073</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.31359</v>
+        <v>0.20256</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.60677</v>
+        <v>0.5273099999999999</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>6.396</v>
+        <v>6.193</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.097</v>
+        <v>-0.073</v>
       </c>
     </row>
     <row r="8">
@@ -631,19 +631,19 @@
         <v>0.7346</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.27401</v>
+        <v>0.17699</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.57844</v>
+        <v>0.50878</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>6.327</v>
+        <v>6.142</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.166</v>
+        <v>-0.125</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         <v>0.6176</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.23036</v>
+        <v>0.1488</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.54713</v>
+        <v>0.48777</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>6.246</v>
+        <v>6.081</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-0.247</v>
+        <v>-0.186</v>
       </c>
     </row>
     <row r="10">
@@ -689,19 +689,19 @@
         <v>0.4996</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.18634</v>
+        <v>0.12036</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.51512</v>
+        <v>0.46552</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>6.159</v>
+        <v>6.013</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0.334</v>
+        <v>-0.253</v>
       </c>
     </row>
     <row r="11">
@@ -718,19 +718,19 @@
         <v>0.38885</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.14502</v>
+        <v>0.09368</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.48404</v>
+        <v>0.44302</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>6.07</v>
+        <v>5.942</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.423</v>
+        <v>-0.324</v>
       </c>
     </row>
     <row r="12">
@@ -747,19 +747,19 @@
         <v>0.29121</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.10861</v>
+        <v>0.07015</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.45475</v>
+        <v>0.42094</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>5.98</v>
+        <v>5.868</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0.513</v>
+        <v>-0.398</v>
       </c>
     </row>
     <row r="13">
@@ -776,19 +776,19 @@
         <v>0.20984</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.07827000000000001</v>
+        <v>0.05056</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.42764</v>
+        <v>0.39973</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>5.891</v>
+        <v>5.794</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0.602</v>
+        <v>-0.473</v>
       </c>
     </row>
     <row r="14">
@@ -805,19 +805,19 @@
         <v>0.14549</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.05428</v>
+        <v>0.03506</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.40281</v>
+        <v>0.37966</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>5.805</v>
+        <v>5.72</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.547</v>
       </c>
     </row>
     <row r="15">
@@ -834,19 +834,19 @@
         <v>0.09705999999999999</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.03622</v>
+        <v>0.02339</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.38015</v>
+        <v>0.36082</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>5.721</v>
+        <v>5.646</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>-0.772</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="16">
@@ -863,19 +863,19 @@
         <v>0.0623</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.02326</v>
+        <v>0.01502</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.35951</v>
+        <v>0.34327</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>5.641</v>
+        <v>5.574</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.852</v>
+        <v>-0.6919999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -892,19 +892,19 @@
         <v>0.03848</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.01436</v>
+        <v>0.00927</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.34069</v>
+        <v>0.32696</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>5.563</v>
+        <v>5.504</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.762</v>
       </c>
     </row>
     <row r="18">
@@ -921,19 +921,19 @@
         <v>0.02286</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.00852</v>
+        <v>0.0055</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.32353</v>
+        <v>0.31183</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>5.489</v>
+        <v>5.436</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-1.004</v>
+        <v>-0.831</v>
       </c>
     </row>
     <row r="19">
@@ -950,19 +950,19 @@
         <v>0.01307</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.00486</v>
+        <v>0.00314</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.30783</v>
+        <v>0.29781</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5.417</v>
+        <v>5.369</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-1.076</v>
+        <v>-0.897</v>
       </c>
     </row>
     <row r="20">
@@ -979,19 +979,19 @@
         <v>0.00719</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.00268</v>
+        <v>0.00173</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.29346</v>
+        <v>0.28482</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>5.348</v>
+        <v>5.305</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-1.145</v>
+        <v>-0.961</v>
       </c>
     </row>
     <row r="21">
@@ -1008,19 +1008,19 @@
         <v>0.00381</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.00142</v>
+        <v>0.00092</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.28028</v>
+        <v>0.27278</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>5.282</v>
+        <v>5.243</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-1.211</v>
+        <v>-1.023</v>
       </c>
     </row>
     <row r="22">
@@ -1037,19 +1037,19 @@
         <v>0.00194</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.00074</v>
+        <v>0.00048</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.26814</v>
+        <v>0.26161</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>5.218</v>
+        <v>5.183</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>-1.275</v>
+        <v>-1.084</v>
       </c>
     </row>
     <row r="23">
@@ -1066,19 +1066,19 @@
         <v>0.00095</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.00037</v>
+        <v>0.00024</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.25695</v>
+        <v>0.25122</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5.157</v>
+        <v>5.124</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-1.336</v>
+        <v>-1.142</v>
       </c>
     </row>
     <row r="24">
@@ -1095,19 +1095,19 @@
         <v>0.00045</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.00017</v>
+        <v>0.00011</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.24661</v>
+        <v>0.24156</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>5.097</v>
+        <v>5.068</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-1.396</v>
+        <v>-1.199</v>
       </c>
     </row>
     <row r="25">
@@ -1124,19 +1124,19 @@
         <v>0.0002</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>8.000000000000001e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.23703</v>
+        <v>0.23257</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>5.04</v>
+        <v>5.013</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-1.453</v>
+        <v>-1.253</v>
       </c>
     </row>
     <row r="26">
@@ -1153,19 +1153,19 @@
         <v>9.000000000000001e-05</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.22814</v>
+        <v>0.22417</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>4.985</v>
+        <v>4.96</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-1.508</v>
+        <v>-1.306</v>
       </c>
     </row>
     <row r="27">
@@ -1185,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.21986</v>
+        <v>0.21632</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>4.932</v>
+        <v>4.908</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.561</v>
+        <v>-1.358</v>
       </c>
     </row>
     <row r="28">
@@ -1214,16 +1214,16 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.21214</v>
+        <v>0.20897</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>4.88</v>
+        <v>4.859</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>-1.613</v>
+        <v>-1.408</v>
       </c>
     </row>
     <row r="29">
@@ -1240,19 +1240,19 @@
         <v>1e-05</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1e-05</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.20493</v>
+        <v>0.20208</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4.83</v>
+        <v>4.81</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.663</v>
+        <v>-1.456</v>
       </c>
     </row>
     <row r="30">
@@ -1272,16 +1272,16 @@
         <v>1e-05</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.19818</v>
+        <v>0.19562</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4.782</v>
+        <v>4.763</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-1.711</v>
+        <v>-1.503</v>
       </c>
     </row>
     <row r="31">
@@ -1301,16 +1301,16 @@
         <v>1e-05</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.19185</v>
+        <v>0.18953</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>4.735</v>
+        <v>4.718</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-1.758</v>
+        <v>-1.548</v>
       </c>
     </row>
     <row r="32">
@@ -1327,19 +1327,19 @@
         <v>0</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1e-05</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.18591</v>
+        <v>0.1838</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>4.69</v>
+        <v>4.674</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>-1.803</v>
+        <v>-1.593</v>
       </c>
     </row>
     <row r="33">
@@ -1359,16 +1359,16 @@
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.18031</v>
+        <v>0.17839</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>4.646</v>
+        <v>4.63</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>-1.847</v>
+        <v>-1.636</v>
       </c>
     </row>
     <row r="34">
@@ -1388,16 +1388,16 @@
         <v>1e-05</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.17503</v>
+        <v>0.17328</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>4.603</v>
+        <v>4.589</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>-1.89</v>
+        <v>-1.678</v>
       </c>
     </row>
     <row r="35">
@@ -1417,16 +1417,16 @@
         <v>1e-05</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.17005</v>
+        <v>0.16845</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4.561</v>
+        <v>4.548</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-1.932</v>
+        <v>-1.718</v>
       </c>
     </row>
     <row r="36">
@@ -1443,19 +1443,19 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1e-05</v>
+        <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.16534</v>
+        <v>0.16387</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>4.521</v>
+        <v>4.508</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-1.972</v>
+        <v>-1.758</v>
       </c>
     </row>
     <row r="37">
@@ -1475,16 +1475,16 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.16088</v>
+        <v>0.15953</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4.482</v>
+        <v>4.469</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>-2.011</v>
+        <v>-1.797</v>
       </c>
     </row>
     <row r="38">
@@ -1504,16 +1504,16 @@
         <v>1e-05</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.15666</v>
+        <v>0.15541</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>4.443</v>
+        <v>4.432</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>-2.05</v>
+        <v>-1.835</v>
       </c>
     </row>
     <row r="39">
@@ -1533,16 +1533,16 @@
         <v>1e-05</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.15264</v>
+        <v>0.1515</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4.406</v>
+        <v>4.395</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>-2.087</v>
+        <v>-1.871</v>
       </c>
     </row>
     <row r="40">
@@ -1562,16 +1562,16 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.14883</v>
+        <v>0.14777</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>4.369</v>
+        <v>4.359</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>-2.124</v>
+        <v>-1.907</v>
       </c>
     </row>
     <row r="41">
@@ -1591,16 +1591,16 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1452</v>
+        <v>0.14421</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>4.334</v>
+        <v>4.324</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-2.159</v>
+        <v>-1.942</v>
       </c>
     </row>
     <row r="42">
@@ -1620,16 +1620,16 @@
         <v>1e-05</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.14174</v>
+        <v>0.14082</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>4.299</v>
+        <v>4.29</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>-2.194</v>
+        <v>-1.977</v>
       </c>
     </row>
     <row r="43">
@@ -1649,16 +1649,16 @@
         <v>1e-05</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.13844</v>
+        <v>0.13759</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>4.265</v>
+        <v>4.256</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>-2.228</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="44">
@@ -1678,16 +1678,16 @@
         <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.13529</v>
+        <v>0.1345</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>4.232</v>
+        <v>4.223</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>-2.261</v>
+        <v>-2.043</v>
       </c>
     </row>
     <row r="45">
@@ -1707,16 +1707,16 @@
         <v>0</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.13228</v>
+        <v>0.13154</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>4.199</v>
+        <v>4.191</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>-2.294</v>
+        <v>-2.075</v>
       </c>
     </row>
     <row r="46">
@@ -1736,16 +1736,16 @@
         <v>1e-05</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.1294</v>
+        <v>0.12871</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>4.168</v>
+        <v>4.16</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>-2.325</v>
+        <v>-2.106</v>
       </c>
     </row>
     <row r="47">
@@ -1765,16 +1765,16 @@
         <v>1e-05</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.12664</v>
+        <v>0.126</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>4.136</v>
+        <v>4.129</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>-2.357</v>
+        <v>-2.137</v>
       </c>
     </row>
     <row r="48">
@@ -1794,16 +1794,16 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.124</v>
+        <v>0.12339</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.106</v>
+        <v>4.099</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>-2.387</v>
+        <v>-2.167</v>
       </c>
     </row>
     <row r="49">
@@ -1823,16 +1823,16 @@
         <v>0</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.12146</v>
+        <v>0.1209</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>4.076</v>
+        <v>4.07</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>-2.417</v>
+        <v>-2.197</v>
       </c>
     </row>
     <row r="50">
@@ -1852,16 +1852,16 @@
         <v>1e-05</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.11903</v>
+        <v>0.1185</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>4.047</v>
+        <v>4.041</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>-2.446</v>
+        <v>-2.226</v>
       </c>
     </row>
     <row r="51">
@@ -1878,19 +1878,19 @@
         <v>0</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1e-05</v>
+        <v>0</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.11669</v>
+        <v>0.11619</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>4.019</v>
+        <v>4.012</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-2.474</v>
+        <v>-2.254</v>
       </c>
     </row>
     <row r="52">
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.11444</v>
+        <v>0.11397</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>3.99</v>
+        <v>3.984</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>-2.503</v>
+        <v>-2.282</v>
       </c>
     </row>
     <row r="53">
@@ -1939,16 +1939,16 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.11228</v>
+        <v>0.11184</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>3.963</v>
+        <v>3.957</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>-2.53</v>
+        <v>-2.309</v>
       </c>
     </row>
     <row r="54">
@@ -1968,16 +1968,16 @@
         <v>1e-05</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.1102</v>
+        <v>0.10978</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>68.73</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>3.936</v>
+        <v>3.93</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>-2.557</v>
+        <v>-2.336</v>
       </c>
     </row>
   </sheetData>
@@ -2036,13 +2036,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3.93</v>
+        <v>4.69</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.491</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="5">
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6.97</v>
+        <v>8.31</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.872</v>
+        <v>1.039</v>
       </c>
     </row>
     <row r="6">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.78</v>
+        <v>0.62</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.89</v>
+        <v>3.09</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.486</v>
+        <v>0.387</v>
       </c>
     </row>
   </sheetData>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>6.49 [--]</t>
+          <t>6.27 [--]</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>0.6492 [--]</t>
+          <t>0.5547 [--]</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>0.3730 [--]</t>
+          <t>0.2409 [--]</t>
         </is>
       </c>
     </row>
